--- a/docs/oc-regiones/alimentos/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/alimentos/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3679.03</v>
+        <v>3647.87</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1332.54</v>
+        <v>1325.7</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2151.87</v>
+        <v>2130.39</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2597.62</v>
+        <v>2571.7</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8932.889999999999</v>
+        <v>8843.74</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10476.73</v>
+        <v>10372.17</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7929.49</v>
+        <v>7850.35</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1444.06</v>
+        <v>1429.64</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2159.51</v>
+        <v>2137.96</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10127.85</v>
+        <v>10026.77</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1519.64</v>
+        <v>1504.47</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2942.29</v>
+        <v>2911.48</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4219.31</v>
+        <v>4196.25</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1221.63</v>
+        <v>1214.95</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1678.16</v>
+        <v>1668.99</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>985.65</v>
+        <v>980.26</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4337.51</v>
+        <v>4313.8</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>745.3</v>
+        <v>741.23</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1027.82</v>
+        <v>1016.37</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1379.5</v>
+        <v>1364.13</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1603.08</v>
+        <v>1585.22</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2093.84</v>
+        <v>2070.51</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1335.37</v>
+        <v>1320.49</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3554.61</v>
+        <v>3515.01</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1353.86</v>
+        <v>1346.45</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3037.38</v>
+        <v>3020.75</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>858.61</v>
+        <v>853.91</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1578.84</v>
+        <v>1570.2</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1386.73</v>
+        <v>1379.14</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>818.4299999999999</v>
+        <v>817.39</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1697.47</v>
+        <v>1695.3</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>758.9</v>
+        <v>767.15</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2940.16</v>
+        <v>2972.13</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>759.84</v>
+        <v>772.96</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1428.77</v>
+        <v>1438.67</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2521.31</v>
+        <v>2539.49</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2625.26</v>
+        <v>2620.6</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>22562.74</v>
+        <v>22522.72</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1085.48</v>
+        <v>1083.55</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1174.83</v>
+        <v>1172.75</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3546.02</v>
+        <v>3539.73</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>13512.83</v>
+        <v>13488.87</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>755.8</v>
+        <v>754.46</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2673.3</v>
+        <v>2662.28</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2837.39</v>
+        <v>2852.04</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4517.14</v>
+        <v>4540.47</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>918.35</v>
+        <v>906.48</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1350.19</v>
+        <v>1332.73</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4064.53</v>
+        <v>4012.9</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>974.72</v>
+        <v>962.34</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7182.89</v>
+        <v>7091.65</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2799.94</v>
+        <v>2764.37</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3260.78</v>
+        <v>3219.36</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2099.88</v>
+        <v>2073.2</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1089.37</v>
+        <v>1075.53</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>14767.81</v>
+        <v>14580.23</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8066.61</v>
+        <v>7964.15</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>862.51</v>
+        <v>851.55</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4695.66</v>
+        <v>4636.02</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1773.16</v>
+        <v>1750.63</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9270.15</v>
+        <v>9152.4</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>826.17</v>
+        <v>817.95</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1637.23</v>
+        <v>1620.94</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2180.02</v>
+        <v>2172.21</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1149.36</v>
+        <v>1145.24</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3068.67</v>
+        <v>3057.67</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1132.4</v>
+        <v>1119.3</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1489.37</v>
+        <v>1476.75</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1255.68</v>
+        <v>1245.05</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>847.48</v>
+        <v>850.73</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>809.8200000000001</v>
+        <v>812.9299999999999</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2730.3</v>
+        <v>2740.78</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2603.4</v>
+        <v>2613.39</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1324.22</v>
+        <v>1329.3</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2637.53</v>
+        <v>2649.48</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2581.42</v>
+        <v>2593.12</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5112.86</v>
+        <v>5126.42</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1145.89</v>
+        <v>1148.93</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>772.46</v>
+        <v>774.51</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1953.54</v>
+        <v>1958.72</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1656.47</v>
+        <v>1660.87</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3934.56</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>10493.74</v>
+        <v>10521.57</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6860.2</v>
+        <v>6907.42</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8002.64</v>
+        <v>8057.73</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1259.85</v>
+        <v>1268.53</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8329.790000000001</v>
+        <v>8387.120000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7835.05</v>
+        <v>7902.01</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7641.65</v>
+        <v>7735.57</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1299.62</v>
+        <v>1306.73</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>901.49</v>
+        <v>906.42</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>47328.17</v>
+        <v>47587</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4115.21</v>
+        <v>4137.71</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>11383.07</v>
+        <v>11445.32</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8423.879999999999</v>
+        <v>8469.950000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>798.3200000000001</v>
+        <v>802.6799999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2623.63</v>
+        <v>2556.63</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2607.37</v>
+        <v>2546.38</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1121.04</v>
+        <v>1104.89</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1879.99</v>
+        <v>1852.9</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>45984.37</v>
+        <v>45390.05</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>13481.35</v>
+        <v>13307.11</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7510.93</v>
+        <v>7413.86</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1714.75</v>
+        <v>1692.59</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6668.39</v>
+        <v>6655.25</v>
       </c>
     </row>
     <row r="107">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1160.68</v>
+        <v>1160.69</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6770.45</v>
+        <v>6770.49</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>9955.139999999999</v>
+        <v>9968.959999999999</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>18100.25</v>
+        <v>18125.38</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1186.61</v>
+        <v>1185.8</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2991.97</v>
+        <v>2981.7</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>17696.77</v>
+        <v>17636.03</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>803.79</v>
+        <v>801.03</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2381.98</v>
+        <v>2373.81</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3018.31</v>
+        <v>3007.95</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>33758.61</v>
+        <v>33642.74</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1286.83</v>
+        <v>1282.41</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>804.64</v>
+        <v>801.88</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>794.45</v>
+        <v>791.73</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>997.36</v>
+        <v>993.9299999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>802.9299999999999</v>
+        <v>800.17</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1090.96</v>
+        <v>1087.22</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>908.91</v>
+        <v>905.79</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1262.49</v>
+        <v>1255.82</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>9636.209999999999</v>
+        <v>9585.309999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1787.17</v>
+        <v>1775.97</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6310.58</v>
+        <v>6271.04</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>24309.9</v>
+        <v>24157.56</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>5576.81</v>
+        <v>5541.86</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1532.12</v>
+        <v>1522.52</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>15193.24</v>
+        <v>15098.03</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6314.86</v>
+        <v>6399.89</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>6477.57</v>
+        <v>6635.09</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3271.06</v>
+        <v>3353.75</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>5426.88</v>
+        <v>5564.08</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1479.15</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2442.35</v>
+        <v>2516.41</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1926.55</v>
+        <v>1984.96</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1161.29</v>
+        <v>1195.81</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3095.65</v>
+        <v>3084.63</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>15186.78</v>
+        <v>15132.71</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3720.56</v>
+        <v>3707.32</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4225.57</v>
+        <v>4193.95</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1544.35</v>
+        <v>1532.79</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5430.78</v>
+        <v>5446.51</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4636.92</v>
+        <v>4650.36</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>833.24</v>
+        <v>835.65</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1326.07</v>
+        <v>1338.14</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1103.5</v>
+        <v>1113.54</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2141.95</v>
+        <v>2161.43</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5670.23</v>
+        <v>5721.81</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5733.09</v>
+        <v>5785.23</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1061.18</v>
+        <v>1070.83</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1591.78</v>
+        <v>1606.25</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3341.34</v>
+        <v>3371.73</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1624.49</v>
+        <v>1639.26</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>939.72</v>
+        <v>948.27</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1436.92</v>
+        <v>1446.92</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1969.7</v>
+        <v>1982.67</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>16696.64</v>
+        <v>16806.6</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1012.65</v>
+        <v>1019.32</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1251.71</v>
+        <v>1259.95</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3068.14</v>
+        <v>3088.35</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>34338.48</v>
+        <v>34564.63</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>854.39</v>
+        <v>860.02</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1385.33</v>
+        <v>1394.45</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1344.54</v>
+        <v>1356.52</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6391.78</v>
+        <v>6448.71</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2053.31</v>
+        <v>2071.6</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3588.08</v>
+        <v>3620.04</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1068.75</v>
+        <v>1078.26</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1804.89</v>
+        <v>1820.96</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>6418.74</v>
+        <v>6475.91</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>11704.78</v>
+        <v>11809.03</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>14037.66</v>
+        <v>14162.69</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>6654.74</v>
+        <v>6714.01</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>28693.58</v>
+        <v>28644.41</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>835.4</v>
+        <v>834.54</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1847.23</v>
+        <v>1845.33</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>825.97</v>
+        <v>820.05</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>8842.040000000001</v>
+        <v>8829.030000000001</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1462.95</v>
+        <v>1460.8</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1790.11</v>
+        <v>1779.56</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>24432.06</v>
+        <v>24288.08</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2712.12</v>
+        <v>2695.64</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>5056.05</v>
+        <v>5036.53</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1412.4</v>
+        <v>1406.95</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>897.4</v>
+        <v>902.05</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>9053.549999999999</v>
+        <v>9100.42</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1903.74</v>
+        <v>1905.58</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>25446.01</v>
+        <v>25470.53</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1217.35</v>
+        <v>1218.52</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2018.51</v>
+        <v>2020.46</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>20807.49</v>
+        <v>20827.54</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>11957.54</v>
+        <v>11969.07</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7496.35</v>
+        <v>7503.57</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4524.64</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3742.86</v>
+        <v>3908.15</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>40285.72</v>
+        <v>42064.81</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>10141.77</v>
+        <v>10589.65</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5962.56</v>
+        <v>6225.88</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4645.92</v>
+        <v>4851.09</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3471.49</v>
+        <v>3528.7</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>5552.39</v>
+        <v>5643.9</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1312.6</v>
+        <v>1315.83</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1570.89</v>
+        <v>1559.8</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>7135.71</v>
+        <v>7085.36</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4902.11</v>
+        <v>4867.52</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4246.65</v>
+        <v>4323.65</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1184.2</v>
+        <v>1205.68</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3291.18</v>
+        <v>3291.01</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>775.9299999999999</v>
+        <v>775.89</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>783.11</v>
+        <v>783.0700000000001</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2676.71</v>
+        <v>2664.74</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2492.49</v>
+        <v>2481.35</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>6478.91</v>
+        <v>6449.94</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>8964.91</v>
+        <v>8972.629999999999</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4662.97</v>
+        <v>4666.98</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>19078.28</v>
+        <v>18858.04</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2570.74</v>
+        <v>2532.4</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2462.05</v>
+        <v>2425.33</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1266.7</v>
+        <v>1247.8</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1889.89</v>
+        <v>1861.7</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2532.58</v>
+        <v>2494.81</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2221.12</v>
+        <v>2187.99</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5286.83</v>
+        <v>5207.97</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1264.37</v>
+        <v>1245.51</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2906.71</v>
+        <v>2863.36</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>16121.01</v>
+        <v>16028.41</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1106.57</v>
+        <v>1100.22</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>20584.81</v>
+        <v>20466.57</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1517.74</v>
+        <v>1508.02</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>5489.27</v>
+        <v>5465.62</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>6519.91</v>
+        <v>6491.82</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1982.38</v>
+        <v>1973.84</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3034.73</v>
+        <v>3021.66</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1113.73</v>
+        <v>1097.62</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>792.86</v>
+        <v>781.39</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1038.58</v>
+        <v>1014.42</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2464.14</v>
+        <v>2406.8</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>18244.68</v>
+        <v>17820.15</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>25456.2</v>
+        <v>24863.85</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>5885.77</v>
+        <v>5748.81</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6962.93</v>
+        <v>6740.91</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1226.44</v>
+        <v>1187.33</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1437.16</v>
+        <v>1399.32</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2853.82</v>
+        <v>2778.67</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2274.55</v>
+        <v>2233.3</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>18689.07</v>
+        <v>18350.15</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1701.77</v>
+        <v>1656.21</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1158.28</v>
+        <v>1127.26</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1340.29</v>
+        <v>1344.19</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>13749.22</v>
+        <v>13789.24</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>987.12</v>
+        <v>989.99</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4021.83</v>
+        <v>4055.96</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>5028.19</v>
+        <v>5070.86</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>3354.55</v>
+        <v>3399.2</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1007.92</v>
+        <v>1021.34</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>20540.44</v>
+        <v>20813.89</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>11593.67</v>
+        <v>11744.97</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5255.79</v>
+        <v>5324.38</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3663.33</v>
+        <v>3711.13</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3579.07</v>
+        <v>3625.78</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>5051.09</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2968.22</v>
+        <v>3006.95</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1749.44</v>
+        <v>1772.27</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>6406.09</v>
+        <v>6489.69</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>13354.7</v>
+        <v>13683.36</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1279.82</v>
+        <v>1304.03</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>791.89</v>
+        <v>806.86</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>15921.62</v>
+        <v>16102.68</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1664.4</v>
+        <v>1683.33</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>8555.440000000001</v>
+        <v>8590.9</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1319.49</v>
+        <v>1324.96</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>14634.16</v>
+        <v>14664.48</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2500.96</v>
+        <v>2506.14</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>833.42</v>
+        <v>835.15</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1487.83</v>
+        <v>1490.91</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1308.14</v>
+        <v>1310.85</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>22263.2</v>
+        <v>22309.32</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3013.08</v>
+        <v>3019.32</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1125.14</v>
+        <v>1120.31</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1017.91</v>
+        <v>1013.54</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>805.41</v>
+        <v>794.46</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>5334</v>
+        <v>5288.5</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1819.12</v>
+        <v>1828.92</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1495.52</v>
+        <v>1512.25</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1452.3</v>
+        <v>1463.3</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>832.3200000000001</v>
+        <v>838.63</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1180.61</v>
+        <v>1191.83</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2833.95</v>
+        <v>2860.87</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2056.51</v>
+        <v>2076.05</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>782.48</v>
+        <v>789.91</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1258.66</v>
+        <v>1246.11</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>970.99</v>
+        <v>961.3099999999999</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3312.6</v>
+        <v>3279.57</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3776.62</v>
+        <v>3738.96</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>8873.6</v>
+        <v>8785.110000000001</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>6235.88</v>
+        <v>6168.04</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>7655.27</v>
+        <v>7571.99</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1111.81</v>
+        <v>1099.71</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1535.85</v>
+        <v>1519.15</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>21099.21</v>
+        <v>21202.85</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>789.5700000000001</v>
+        <v>793.45</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>8266.719999999999</v>
+        <v>8307.33</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>6884.42</v>
+        <v>6918.23</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2009.27</v>
+        <v>2015.67</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>14027.01</v>
+        <v>14071.65</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>5915.53</v>
+        <v>5934.35</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>930.71</v>
+        <v>933.67</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>896.35</v>
+        <v>899.21</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1733.15</v>
+        <v>1738.66</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>20252.71</v>
+        <v>20360.4</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2269.72</v>
+        <v>2281.79</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>17681.22</v>
+        <v>17934.22</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>7916.52</v>
+        <v>8029.8</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1472.86</v>
+        <v>1493.93</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1258.81</v>
+        <v>1280.1</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1081.07</v>
+        <v>1091.21</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2680.63</v>
+        <v>2660.3</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1006.05</v>
+        <v>991.77</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1161.61</v>
+        <v>1145.64</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1950.72</v>
+        <v>1923.92</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>3271.9</v>
+        <v>3226.94</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>20703.82</v>
+        <v>20575.46</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2286.41</v>
+        <v>2320.46</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2782.67</v>
+        <v>2824.11</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>14804.71</v>
+        <v>15025.15</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2784.79</v>
+        <v>2826.26</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2504.79</v>
+        <v>2552.41</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1605.01</v>
+        <v>1635.53</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1040.62</v>
+        <v>1064.09</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>940.91</v>
+        <v>962.13</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1175.58</v>
+        <v>1202.09</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1983.33</v>
+        <v>1997.03</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3353.08</v>
+        <v>3376.23</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1289.55</v>
+        <v>1298.45</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1838.11</v>
+        <v>1843.79</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2514.99</v>
+        <v>2481.49</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>14701.41</v>
+        <v>14483.6</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1325.89</v>
+        <v>1306.25</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2699.14</v>
+        <v>2659.15</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>891.98</v>
+        <v>878.76</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1215.43</v>
+        <v>1197.42</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2789.25</v>
+        <v>2731.93</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>3553.26</v>
+        <v>3480.24</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>27335.46</v>
+        <v>26773.67</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1408.75</v>
+        <v>1415.92</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3704.74</v>
+        <v>3723.62</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>9405.09</v>
+        <v>9441.709999999999</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1127.06</v>
+        <v>1131.45</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1051.24</v>
+        <v>1055.33</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>829.85</v>
+        <v>825.65</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>990.21</v>
+        <v>985.2</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>807.03</v>
+        <v>812.29</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>7985.18</v>
+        <v>8037.24</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>772.1</v>
+        <v>777.13</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2077.49</v>
+        <v>2091.04</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>991.72</v>
+        <v>993.99</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>780.22</v>
+        <v>782.01</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>6914.76</v>
+        <v>6930.61</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>7514.9</v>
+        <v>7532.14</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1866.29</v>
+        <v>1878.79</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1393.2</v>
+        <v>1402.52</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1151.13</v>
+        <v>1158.84</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>5652.41</v>
+        <v>5690.24</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>6134.95</v>
+        <v>6177.88</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>5205.85</v>
+        <v>5242.28</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1305.88</v>
+        <v>1315.02</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1091.72</v>
+        <v>1099.36</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4324.52</v>
+        <v>4354.79</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>4746.38</v>
+        <v>4736.06</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2748.75</v>
+        <v>2743.24</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>6995.84</v>
+        <v>6981.82</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1575.34</v>
+        <v>1572.18</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>980.6</v>
+        <v>978.64</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1979.43</v>
+        <v>1967.97</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>6691.19</v>
+        <v>6583.21</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>787.9</v>
+        <v>775.1900000000001</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3071.16</v>
+        <v>3021.6</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1811.66</v>
+        <v>1790.58</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1016.34</v>
+        <v>1004.52</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1146.5</v>
+        <v>1133.16</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>3382.52</v>
+        <v>3343.16</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1398.63</v>
+        <v>1382.35</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>4530.33</v>
+        <v>4505.21</v>
       </c>
     </row>
   </sheetData>
